--- a/human_validation/judge/kor/judge_D011_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D011_S003_P002__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,376 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오셨는지 말씀해주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 이제는 정말 머릿속을 끌 수가 없어서 왔어요. 고객이 답장을 안 한다든가 하는 사소한 일에서 시작되는데, 몇 분 안에 저는 계약을 잃고, 이혼 관련 지급금이 밀리고, 다시는 진짜 리더십 자리로 돌아가지 못할 거라는 생각까지 하고 있어요. 그게 계속 이어지고, 저는 그걸 멈출 수가 없는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 당장 급한 문제가 없을 때조차 곤두서 있거나 긴장하거나 지나치게 걱정하는 느낌이 자주 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 급한 일이 전혀 없을 때조차 거의 하루 종일 긴장된 느낌이에요. 어깨가 계속 뻣뻣하고, 나쁜 소식에 대비하고 있는 것 같아요, 그리고 저도 모르게 집 안을 서성이거나 통화하면서 별 이유 없이 다리를 떨고 있는 걸 발견하곤 해요. 마치 무슨 일이 일어나기도 전에 몸이 이미 긴장해 있는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 뚜렷한 이유가 없는데도 기분이 가라앉거나 슬프거나, 예전에 즐기던 것들에 흥미를 잃은 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 딱히 이유 없이 슬프다고는 말 못 하겠고, 그런 식으로 생각해본 적도 딱히 없어요. 그냥 많이 지쳐 있는 것 같기는 한데, 그걸 흥미를 잃었다고 할 수 있는지는 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 다 괜찮은 상황인데도, 하루 이틀 정도라도 기분이 가라앉거나 예전에 즐기던 활동에서 즐거움을 잃은 걸 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 그런 식으로는 딱히 알아챈 적이 없어요. 그러니까, 지치고 산만해지긴 하는데, 다른 모든 게 괜찮은데 그냥 가라앉거나 즐겁지 않은 특정한 날들이 있었다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 특별히 스트레스받거나 걱정하고 있지 않을 때도, 며칠 이상 기분이 가라앉거나 흥미를 잃은 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 그런 적은 없는 것 같아요. 스트레스받거나 걱정하지 않으면서도 며칠 동안 가라앉거나 즐거움을 잃었던 시기를 딱히 짚을 수가 없어요. 솔직히 그걸 따로 구분하기가 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 적극적으로 스트레스를 받거나 걱정하고 있지 않을 때, 공허하거나 무기력하거나 예전만큼 즐겁지 않은 느낌이 드는 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 그런 것 같지는 않아요. 스트레스받거나 걱정하지 않을 때는 공허하거나 뭔가가 즐겁지 않다는 걸 보통 못 느껴요. 피곤할 수는 있는데, 그것만 따로 그런 느낌을 받은 적이 있다고는 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 스트레스받거나 걱정할 만한 일이 없을 때조차 기분이 가라앉거나 흥미를 잃거나, 평소 즐기던 활동에서 즐거움을 느끼지 못한 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 아니요, 그런 건 못 느낀 것 같아요. 스트레스받거나 걱정할 일이 없으면, 딱히 가라앉거나 뭔가를 즐기지 못한다고는 말 못 하겠어요. 그런 느낌이 든다면, 그건 보통 뭔가에 대해 걱정하는 것과 연결돼 있는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 스트레스받거나 걱정할 일이 없을 때도 기분이 가라앉거나, 흥미를 잃거나, 평소 좋아하던 활동을 즐기지 못한 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 딱히 짚을 수 있는 건 없어요. 제가 가라앉거나 뭔가를 즐기지 못한다면, 보통은 뭔가 걱정하거나 스트레스받고 있어서 그런 거예요. 그냥 아무 이유 없이 그랬던 기억은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 스트레스받거나 걱정할 일이 전혀 없을 때도, 여전히 기분이 가라앉거나, 흥미를 잃거나, 평소 즐기던 활동에서 즐거움을 못 느끼는 걸 알아챈 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 아니요, 그런 게 저절로 일어나는 걸 딱히 못 느꼈어요. 가라앉거나 흥미가 줄어든다면, 그건 뭔가에 스트레스받거나 걱정하는 것과 연결돼 있는 것 같아요. 다른 게 다 괜찮은데 그런 느낌이 들었던 때는 떠오르지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 스트레스받거나 걱정할 일이 없을 때도, 적어도 며칠 동안 기분이 가라앉거나, 흥미를 잃거나, 평소 좋아하던 활동을 즐기지 못한 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 없는 것 같아요. 그런 식으로는 딱히 구분이 안 돼요—며칠 동안 가라앉거나 뭔가를 즐기지 못한다면, 보통 거기엔 걱정이나 스트레스가 얽혀 있어요. 걱정하는 것 없이 그런 일이 일어났던 기억은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 특별히 스트레스받거나 걱정하지 않을 때조차, 2주 이상 기분이 가라앉거나 흥미를 잃거나 활동을 즐기지 못했던 시기가 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 아니요, 그런 적은 없는 것 같아요. 가라앉거나 뭔가를 즐기지 못한다면, 보통 걱정이나 스트레스와 얽혀 있어요. 그게 없었던 2주 동안의 시기는 떠오르지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 인생에서 특별히 스트레스받거나 걱정하지 않을 때조차, 적어도 2주 동안 기분이 가라앉거나, 흥미를 잃거나, 평소 좋아하던 활동을 즐기지 못했던 때가 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 그런 2주 동안의 시기는 없었던 것 같아요. 가라앉거나 뭔가에 흥미가 없을 때는 늘 걱정이나 스트레스와 얽혀 있었어요. 그게 없었던 때는 딱히 생각나지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 특별히 스트레스받거나 걱정하지 않을 때조차, 거의 매일 적어도 2주 동안 기분이 가라앉거나 흥미를 잃었던 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 아니요, 딱히요. 스트레스나 걱정이 없는 상태에서 거의 매일 2주 동안 가라앉거나 흥미가 없었던 그런 시기는 없었던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 특별히 스트레스받거나 걱정할 일이 없을 때도, 거의 매일 2주 이상 기분이 가라앉거나 흥미를 잃었던 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 없는 것 같아요. 이미 얘기했던 것 같긴 한데, 뭔가 스트레스나 걱정되는 일 없이 그냥 2주 동안 가라앉거나 흥미가 없었던 그런 시기는 기억이 안 나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 특별히 스트레스받거나 걱정할 일이 없을 때도, 거의 매일 2주 이상 기분이 가라앉거나 흥미를 잃었던 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 여전히 그런 예가 떠오르지 않아요. 가라앉거나 흥미를 잃은 적이 있었다면, 보통 뭔가 걱정하거나 스트레스받고 있어서였지, 그냥 아무 이유 없이 2주 이상 그랬던 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 스트레스받거나 걱정할 일이 전혀 없을 때도, 거의 매일 흥미를 잃거나 기분이 가라앉는 2주 이상의 시기가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 없는 것 같아요. 기분이 가라앉거나 흥미가 없을 때는 스트레스나 걱정과 얽혀 있었어요. 그런 게 없이 일어난 2주 동안의 시기는 떠오르지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 특별히 스트레스받거나 걱정할 일이 없을 때도, 거의 매일 2주 이상 기분이 가라앉거나 흥미를 잃었던 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 그런 것 같지 않아요. 몇 번 대답드린 건 아는데, 정말로 스트레스나 걱정 없이 그런 시기가 있었다고는 짚어낼 수가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>진단명: 범불안장애 (D011)
 인구통계: 성별 남성 / 나이 47 / 직업상태 computer or information systems manager / 최종학력 학사
@@ -575,425 +936,36 @@
 증상 지속 기간: 1 year and 1 months
 추가 요건: 
 주호소 증상 코드: S057
-배경 서술: 돈은 디지털 전환 프로젝트가 일정을 초과하고 경영진이 눈에 띄는 인사 조치를 결정하면서, 13개월 전 IT 관리직 고위직에서 해고되었다. 처음에는 곧 다시 자리를 잡을 거라 기대했지만, 걱정은 실직에서 재정 문제, 베데스다 기술업계에서의 평판, 향후 CIO가 될 가능성, 이혼 관련 의무, 그리고 면접에서의 침묵 하나하나가 영구적인 실패를 의미하는 건 아닌지까지 번져갔다. 몇 달이 지나면서 그는 잠을 제대로 못 잤고, 몸이 계속 긴장 상태였으며, 걱정을 거의 통제할 수 없다고 느꼈고, 친구들과 축구 동호회 사람들, 가족에게 예민하게 짜증을 내게 되었으며, 결국 네트워킹 마감을 놓치고 평소 그를 지탱해주던 활동들에서 멀어지게 되었다. 그는 계약직 일자리를 구한 뒤에도 계속되는 불안감과 기능 저하가 해소되지 않는다는 것을 깨닫고 스스로 정신과 진료를 받았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오셨는지 말씀해주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 이제는 정말 머릿속을 끌 수가 없어서 왔어요. 고객이 답장을 안 한다든가 하는 사소한 일에서 시작되는데, 몇 분 안에 저는 계약을 잃고, 이혼 관련 지급금이 밀리고, 다시는 진짜 리더십 자리로 돌아가지 못할 거라는 생각까지 하고 있어요. 그게 계속 이어지고, 저는 그걸 멈출 수가 없는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 당장 급한 문제가 없을 때조차 곤두서 있거나 긴장하거나 지나치게 걱정하는 느낌이 자주 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 급한 일이 전혀 없을 때조차 거의 하루 종일 긴장된 느낌이에요. 어깨가 계속 뻣뻣하고, 나쁜 소식에 대비하고 있는 것 같아요, 그리고 저도 모르게 집 안을 서성이거나 통화하면서 별 이유 없이 다리를 떨고 있는 걸 발견하곤 해요. 마치 무슨 일이 일어나기도 전에 몸이 이미 긴장해 있는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 뚜렷한 이유가 없는데도 기분이 가라앉거나 슬프거나, 예전에 즐기던 것들에 흥미를 잃은 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 딱히 이유 없이 슬프다고는 말 못 하겠고, 그런 식으로 생각해본 적도 딱히 없어요. 그냥 많이 지쳐 있는 것 같기는 한데, 그걸 흥미를 잃었다고 할 수 있는지는 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 다 괜찮은 상황인데도, 하루 이틀 정도라도 기분이 가라앉거나 예전에 즐기던 활동에서 즐거움을 잃은 걸 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 그런 식으로는 딱히 알아챈 적이 없어요. 그러니까, 지치고 산만해지긴 하는데, 다른 모든 게 괜찮은데 그냥 가라앉거나 즐겁지 않은 특정한 날들이 있었다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 특별히 스트레스받거나 걱정하고 있지 않을 때도, 며칠 이상 기분이 가라앉거나 흥미를 잃은 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 그런 적은 없는 것 같아요. 스트레스받거나 걱정하지 않으면서도 며칠 동안 가라앉거나 즐거움을 잃었던 시기를 딱히 짚을 수가 없어요. 솔직히 그걸 따로 구분하기가 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 적극적으로 스트레스를 받거나 걱정하고 있지 않을 때, 공허하거나 무기력하거나 예전만큼 즐겁지 않은 느낌이 드는 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 그런 것 같지는 않아요. 스트레스받거나 걱정하지 않을 때는 공허하거나 뭔가가 즐겁지 않다는 걸 보통 못 느껴요. 피곤할 수는 있는데, 그것만 따로 그런 느낌을 받은 적이 있다고는 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 스트레스받거나 걱정할 만한 일이 없을 때조차 기분이 가라앉거나 흥미를 잃거나, 평소 즐기던 활동에서 즐거움을 느끼지 못한 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 아니요, 그런 건 못 느낀 것 같아요. 스트레스받거나 걱정할 일이 없으면, 딱히 가라앉거나 뭔가를 즐기지 못한다고는 말 못 하겠어요. 그런 느낌이 든다면, 그건 보통 뭔가에 대해 걱정하는 것과 연결돼 있는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 스트레스받거나 걱정할 일이 없을 때도 기분이 가라앉거나, 흥미를 잃거나, 평소 좋아하던 활동을 즐기지 못한 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 딱히 짚을 수 있는 건 없어요. 제가 가라앉거나 뭔가를 즐기지 못한다면, 보통은 뭔가 걱정하거나 스트레스받고 있어서 그런 거예요. 그냥 아무 이유 없이 그랬던 기억은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 스트레스받거나 걱정할 일이 전혀 없을 때도, 여전히 기분이 가라앉거나, 흥미를 잃거나, 평소 즐기던 활동에서 즐거움을 못 느끼는 걸 알아챈 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 아니요, 그런 게 저절로 일어나는 걸 딱히 못 느꼈어요. 가라앉거나 흥미가 줄어든다면, 그건 뭔가에 스트레스받거나 걱정하는 것과 연결돼 있는 것 같아요. 다른 게 다 괜찮은데 그런 느낌이 들었던 때는 떠오르지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 스트레스받거나 걱정할 일이 없을 때도, 적어도 며칠 동안 기분이 가라앉거나, 흥미를 잃거나, 평소 좋아하던 활동을 즐기지 못한 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 없는 것 같아요. 그런 식으로는 딱히 구분이 안 돼요—며칠 동안 가라앉거나 뭔가를 즐기지 못한다면, 보통 거기엔 걱정이나 스트레스가 얽혀 있어요. 걱정하는 것 없이 그런 일이 일어났던 기억은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 특별히 스트레스받거나 걱정하지 않을 때조차, 2주 이상 기분이 가라앉거나 흥미를 잃거나 활동을 즐기지 못했던 시기가 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 아니요, 그런 적은 없는 것 같아요. 가라앉거나 뭔가를 즐기지 못한다면, 보통 걱정이나 스트레스와 얽혀 있어요. 그게 없었던 2주 동안의 시기는 떠오르지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 인생에서 특별히 스트레스받거나 걱정하지 않을 때조차, 적어도 2주 동안 기분이 가라앉거나, 흥미를 잃거나, 평소 좋아하던 활동을 즐기지 못했던 때가 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 그런 2주 동안의 시기는 없었던 것 같아요. 가라앉거나 뭔가에 흥미가 없을 때는 늘 걱정이나 스트레스와 얽혀 있었어요. 그게 없었던 때는 딱히 생각나지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 특별히 스트레스받거나 걱정하지 않을 때조차, 거의 매일 적어도 2주 동안 기분이 가라앉거나 흥미를 잃었던 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 아니요, 딱히요. 스트레스나 걱정이 없는 상태에서 거의 매일 2주 동안 가라앉거나 흥미가 없었던 그런 시기는 없었던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 특별히 스트레스받거나 걱정할 일이 없을 때도, 거의 매일 2주 이상 기분이 가라앉거나 흥미를 잃었던 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 없는 것 같아요. 이미 얘기했던 것 같긴 한데, 뭔가 스트레스나 걱정되는 일 없이 그냥 2주 동안 가라앉거나 흥미가 없었던 그런 시기는 기억이 안 나요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 특별히 스트레스받거나 걱정할 일이 없을 때도, 거의 매일 2주 이상 기분이 가라앉거나 흥미를 잃었던 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 여전히 그런 예가 떠오르지 않아요. 가라앉거나 흥미를 잃은 적이 있었다면, 보통 뭔가 걱정하거나 스트레스받고 있어서였지, 그냥 아무 이유 없이 2주 이상 그랬던 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 스트레스받거나 걱정할 일이 전혀 없을 때도, 거의 매일 흥미를 잃거나 기분이 가라앉는 2주 이상의 시기가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 없는 것 같아요. 기분이 가라앉거나 흥미가 없을 때는 스트레스나 걱정과 얽혀 있었어요. 그런 게 없이 일어난 2주 동안의 시기는 떠오르지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 특별히 스트레스받거나 걱정할 일이 없을 때도, 거의 매일 2주 이상 기분이 가라앉거나 흥미를 잃었던 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 그런 것 같지 않아요. 몇 번 대답드린 건 아는데, 정말로 스트레스나 걱정 없이 그런 시기가 있었다고는 짚어낼 수가 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
+배경 서술: 돈은 디지털 전환 프로젝트가 일정을 초과하고 경영진이 눈에 띄는 인사 조치를 결정하면서, 13개월 전 IT 관리직 고위직에서 해고되었다. 처음에는 곧 다시 자리를 잡을 거라 기대했지만, 걱정은 실직에서 재정 문제, 베데스다 기술업계에서의 평판, 향후 CIO가 될 가능성, 이혼 관련 의무, 그리고 면접에서의 침묵 하나하나가 영구적인 실패를 의미하는 건 아닌지까지 번져갔다. 몇 달이 지나면서 그는 잠을 제대로 못 잤고, 몸이 계속 긴장 상태였으며, 걱정을 거의 통제할 수 없다고 느꼈고, 친구들과 축구 동호회 사람들, 가족에게 예민하게 짜증을 내게 되었으며, 결국 네트워킹 마감을 놓치고 평소 그를 지탱해주던 활동들에서 멀어지게 되었다. 그는 계약직 일자리를 구한 뒤에도 계속되는 불안감과 기능 저하가 해소되지 않는다는 것을 깨닫고 스스로 정신과 진료를 받았다.
+표집된 증상 목록:
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S056 과도한 불안/걱정: 여러 사건이나 활동에 대해 과도한 불안과 걱정(예기 불안)이 지속적으로 나타남.
+  - S057 통제 불가능한 걱정: 걱정을 멈추거나 조절하기 어렵다는 주관적 경험.
+  - S058 안절부절/긴장감: 안절부절못하거나 곤두선 느낌 또는 신경이 날카로운 느낌.
+  - S060 과민성: 사소한 자극에도 민감하거나 날카롭게 반응하는 상태.</t>
+        </is>
+      </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 범불안장애 (D011, ICD: F41.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: anxiety_symptoms (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 과도한 불안/걱정: 여러 사건이나 활동에 대해 과도한 불안과 걱정(예기 불안)이 지속적으로 나타남.; 통제 불가능한 걱정: 걱정을 멈추거나 조절하기 어렵다는 주관적 경험.; 안절부절/긴장감: 안절부절못하거나 곤두선 느낌 또는 신경이 날카로운 느낌.
-  누락: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 집중 곤란: 집중하는 데 어려움을 겪거나 머릿속이 하얘짐.; 과민성: 사소한 자극에도 민감하거나 날카롭게 반응하는 상태.; 근육 긴장: 근육이 지속적으로 긴장되고 뻣뻣하며 불편감을 동반하는 상태.</t>
+          <t>의사의 최종 진단: 범불안장애 (D011, ICD: F41.1)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: anxiety_symptoms (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 과도한 불안/걱정: 여러 사건이나 활동에 대해 과도한 불안과 걱정(예기 불안)이 지속적으로 나타남.
+  - 통제 불가능한 걱정: 걱정을 멈추거나 조절하기 어렵다는 주관적 경험.
+  - 안절부절/긴장감: 안절부절못하거나 곤두선 느낌 또는 신경이 날카로운 느낌.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D011_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D011_S003_P002__qwen3-235b_kor.xlsx
@@ -922,6 +922,11 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -961,11 +966,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D011_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D011_S003_P002__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.2912</v>
+        <v>0.5294</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.4706</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.1996</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.6667</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
